--- a/evaluation/evaluation_reports/2025-04-08/overview_2025-04-08.xlsx
+++ b/evaluation/evaluation_reports/2025-04-08/overview_2025-04-08.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/piek/Desktop/d-Leolani/cltl-knowledgeextraction/examples/evaluation_reports/2025-04-08/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/piek/Desktop/d-Leolani/cltl-knowledgeextraction/evaluation/evaluation_reports/2025-04-08/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{51E645ED-23D3-C643-9FDB-002034DAEF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{478B23DC-2C9B-2F44-9EF1-4DD75992B653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="6280" windowWidth="34180" windowHeight="21600" firstSheet="3" activeTab="7" xr2:uid="{AA87EF52-3B62-BB43-AD06-49DBE320B848}"/>
+    <workbookView xWindow="41220" yWindow="1180" windowWidth="34180" windowHeight="21000" activeTab="7" xr2:uid="{AA87EF52-3B62-BB43-AD06-49DBE320B848}"/>
   </bookViews>
   <sheets>
     <sheet name="overview_2025-04-08" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="BERT" sheetId="5" r:id="rId5"/>
     <sheet name="Llama" sheetId="6" r:id="rId6"/>
     <sheet name="Qwen" sheetId="8" r:id="rId7"/>
-    <sheet name="Blad8" sheetId="9" r:id="rId8"/>
+    <sheet name="Errors" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
